--- a/data/trans_orig/P80_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P80_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>364</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>629671</t>
+          <t>683557</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>623447</t>
+          <t>677106</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>633189</t>
+          <t>687875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>674320</t>
+          <t>731126</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>672134</t>
+          <t>727667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>675210</t>
+          <t>732358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1303991</t>
+          <t>1414682</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1296993</t>
+          <t>1406815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1307738</t>
+          <t>1419012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26125</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>32184</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>48803</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1178468</t>
+          <t>1028800</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1166063</t>
+          <t>1015160</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1186552</t>
+          <t>1038125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,17 +1216,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>944332</t>
+          <t>1055216</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>936866</t>
+          <t>1047742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>948802</t>
+          <t>1060510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2122800</t>
+          <t>2084016</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2110614</t>
+          <t>2067397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2133372</t>
+          <t>2095602</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192188</t>
+          <t>1048183</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192188</t>
+          <t>1048183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192188</t>
+          <t>1048183</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>955777</t>
+          <t>1068017</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>955777</t>
+          <t>1068017</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>955777</t>
+          <t>1068017</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2147965</t>
+          <t>2116200</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2147965</t>
+          <t>2116200</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2147965</t>
+          <t>2116200</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34887</t>
+          <t>36328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23083</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29956</t>
+          <t>34722</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17500</t>
+          <t>22630</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48452</t>
+          <t>53064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1524,17 +1524,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>685842</t>
+          <t>781677</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668863</t>
+          <t>765756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>694998</t>
+          <t>791354</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>917738</t>
+          <t>794207</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>906702</t>
+          <t>784398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>925085</t>
+          <t>800780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1603578</t>
+          <t>1575883</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1585082</t>
+          <t>1557541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1616034</t>
+          <t>1587975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703750</t>
+          <t>802084</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703750</t>
+          <t>802084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703750</t>
+          <t>802084</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>929785</t>
+          <t>808522</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>929785</t>
+          <t>808522</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>929785</t>
+          <t>808522</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1633534</t>
+          <t>1610605</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1633534</t>
+          <t>1610605</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1633534</t>
+          <t>1610605</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>32129</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18387</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41868</t>
+          <t>46667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24606</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35609</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>52621</t>
+          <t>58542</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38685</t>
+          <t>44678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68249</t>
+          <t>76480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>897810</t>
+          <t>956814</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>883957</t>
+          <t>942276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>907438</t>
+          <t>967182</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1069081</t>
+          <t>1091257</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1058078</t>
+          <t>1081044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1077861</t>
+          <t>1099778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1966891</t>
+          <t>2048071</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1951263</t>
+          <t>2030133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1980827</t>
+          <t>2061935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925825</t>
+          <t>988943</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925825</t>
+          <t>988943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925825</t>
+          <t>988943</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1093687</t>
+          <t>1117670</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1093687</t>
+          <t>1117670</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1093687</t>
+          <t>1117670</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019512</t>
+          <t>2106613</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019512</t>
+          <t>2106613</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019512</t>
+          <t>2106613</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44958</t>
+          <t>60769</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88555</t>
+          <t>104966</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49148</t>
+          <t>55125</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36004</t>
+          <t>43517</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63275</t>
+          <t>70790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>134197</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91253</t>
+          <t>110562</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141103</t>
+          <t>164756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3391790</t>
+          <t>3450847</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3368649</t>
+          <t>3424953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3412246</t>
+          <t>3469150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3605471</t>
+          <t>3671806</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3591344</t>
+          <t>3656141</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3618615</t>
+          <t>3683414</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6997261</t>
+          <t>7122653</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6970720</t>
+          <t>7092094</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7020570</t>
+          <t>7146288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
